--- a/data/paragraph_hate_speech.xlsx
+++ b/data/paragraph_hate_speech.xlsx
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>0,6b,6c,0,1c,0,0,6c,6c,6c,0,0</t>
+          <t>0,6a,6a,6c,0,6b,6c,0,0,2,6c,6c,6c,0,0,0</t>
         </is>
       </c>
     </row>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>6b,1c,1c,1c,6b,6b,6c,0,6c,0,0</t>
+          <t>6b,0,0,0,0,0,4a,0,0,1c,0</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>1c,1c,1c,1c,1c,1c,0,1c</t>
+          <t>1c,0,1c,0,0,0,0,0</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>0,7,1b,1b,0,1b,1b,1b,1b,0,1b,1b,0,1c</t>
+          <t>0,7,0,1c,0,0,1c,0,1c,6c,7,1c,6c,0,0,6c,1c</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>0,6c,0,1c,0,0,0,0,2,2,6c</t>
+          <t>0,0,0,1c,0,0,0,0,0,0,0</t>
         </is>
       </c>
     </row>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>1c,1c,6c,1c,1c,1c</t>
+          <t>0,0,0,0,0,0</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>0,0,0,1b,1b,0,0,1b,0,0,0,1b,1b,1b,1b,1b,0,1b,1b,1b,6c,0,0,0</t>
+          <t>0,0,0,1b,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,0,6c,0,0,0</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>0,1b,1b,1b,1b,1b,1b</t>
+          <t>0,1c,6a,6c,1b,1c,1b,1c,0,0,0</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>0,6c,1b,1c,0,1b</t>
+          <t>0,1c,6c,1c,1c,1c,0</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>1b,1b,1b,1b,1c,0,0,1c,0,0,0,0,0,0,0,0,0</t>
+          <t>1c,1c,1c,0,0,0,0,0,0,0,0,1c,6c,0,0,0,0,0</t>
         </is>
       </c>
     </row>
@@ -10683,7 +10683,7 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>0,0,0,6a,0,0,6a,0,6a,0,1c,0</t>
+          <t>0,0,0,0,0,0,0,0,0,0,1b,1c</t>
         </is>
       </c>
     </row>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>1c,0,3a,3a,3a</t>
+          <t>3a,0,3a,3a,0</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>0,6b,0,6c,0,0,0,0</t>
+          <t>0,0,1b,0,1b,0,6a,6b,0,0</t>
         </is>
       </c>
     </row>
@@ -12093,7 +12093,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>6a,0,0,0,0,0</t>
+          <t>0,0,0,0,0,0</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>0,0,6b,6b,6b,6b,0,0,1c,0,0,0,0,6b,6b</t>
+          <t>0,0,0,0,0,6b,6c,0,0,0,0,0,0,0,0,0</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>0,0,6c,3b,0,6c,6c,6c,6c,3b,6c,3b,3b</t>
+          <t>0,3b,6c,3b,0,6c,0,4a,4b,6c,0,3b,3b,3b</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13218,7 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>6a,0,0,6b,1c,0,0,0,1c,6c</t>
+          <t>0,0,0,0,0,0,0,0,6c</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>3b,5,0,3b,3b,3b,3b,3b,3b,3b,3b,3b,3b</t>
+          <t>4b,0,0,0,0,0,0,0,0,0,3b,0</t>
         </is>
       </c>
     </row>

--- a/data/paragraph_hate_speech.xlsx
+++ b/data/paragraph_hate_speech.xlsx
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>0,0,1b,0,1b,0,6a,6b,0,0</t>
+          <t>0,0,1b,0,1b,0,6a,6b,0,0,0</t>
         </is>
       </c>
     </row>

--- a/data/paragraph_hate_speech.xlsx
+++ b/data/paragraph_hate_speech.xlsx
@@ -6328,12 +6328,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>jel to onaj momak sto je degeneka slao po cevape kod "junuza",haa cigani??? Da to je bilo onda kada ste svi u paketu isli kod Jonuza na cevape na -30</t>
+          <t>jel to onaj momak sto je degeneka slao po cevape kod "junuza". haa cigani??? Da to je bilo onda kada ste svi u paketu isli kod Jonuza na cevape na -30</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>1b,1b</t>
+          <t>1b,1b,1b</t>
         </is>
       </c>
     </row>
